--- a/xls/square_20_tri3_16.xlsx
+++ b/xls/square_20_tri3_16.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>441</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>3.3942467695947824</v>
+      </c>
+      <c r="J14">
+        <v>0.00032940402537186904</v>
+      </c>
+      <c r="K14">
+        <v>1.0024224457488191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>441</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>2.3788340917265822</v>
+      </c>
+      <c r="J15">
+        <v>-0.7251138869199447</v>
+      </c>
+      <c r="K15">
+        <v>0.45815121535496794</v>
+      </c>
+    </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
